--- a/Result/profitability/8044.xlsx
+++ b/Result/profitability/8044.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,16 +669,16 @@
         <v>0.84</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.87375</v>
+        <v>-0.8062499999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>13.3525</v>
+        <v>13.56</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
@@ -687,7 +687,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.38</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6749999999999999</v>
+        <v>-0.5599999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>13.25375</v>
+        <v>13.775</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.28</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.44125</v>
+        <v>-0.42625</v>
       </c>
       <c r="N4" t="n">
-        <v>13.5875</v>
+        <v>13.89875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.4</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2925</v>
+        <v>-0.23875</v>
       </c>
       <c r="N5" t="n">
-        <v>13.93375</v>
+        <v>14.2125</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.48</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.09499999999999997</v>
+        <v>-0.09624999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>14.125</v>
+        <v>14.33125</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>0.05750000000000004</v>
+        <v>0.235</v>
       </c>
       <c r="N7" t="n">
-        <v>14.21625</v>
+        <v>14.575</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.49</v>
       </c>
       <c r="M8" t="n">
-        <v>0.38</v>
+        <v>0.345</v>
       </c>
       <c r="N8" t="n">
-        <v>14.51875</v>
+        <v>14.55875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8044</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>9362</v>
+      </c>
+      <c r="D75" t="n">
+        <v>7890</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1472</v>
+      </c>
+      <c r="F75" t="n">
+        <v>15.73</v>
+      </c>
+      <c r="G75" t="n">
+        <v>40</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>0.43%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-36</v>
+      </c>
+      <c r="J75" t="n">
+        <v>4</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-136</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-1.0625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>13.80625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.7179487179487181</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.3200000000000003</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.0207657365347178</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.3909090909090909</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1651851851851853</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
